--- a/Mau_Import_Dang_Ky_Hoi_Thao.xlsx
+++ b/Mau_Import_Dang_Ky_Hoi_Thao.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HUONG_DAN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DS_DANG_KY'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DS_DANG_KY'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +42,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00172033"/>
+        <fgColor rgb="000D6EFD"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,14 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,14 +426,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
@@ -462,12 +457,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Danh sách thành viên chi tiết</t>
+          <t>Họ tên thành viên</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mã NV / CCCD đăng ký</t>
+          <t>Mã NV / CCCD thành viên</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -487,87 +482,175 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Đội nhóm</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Đội Ví dụ 01</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Bóng đá</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn A - MNV: NV001 - Phòng ban: Sản xuất - Bộ phận: Ép nhựa | Trần Văn B - MNV: NV002 - Phòng ban: Sản xuất - Bộ phận: Đóng gói</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>NV001;NV002</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Kéo co</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NV001</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Sản xuất</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Ép nhựa</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Khối A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Đội nhóm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Đội Ví dụ 01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Kéo co</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Trần Văn B</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NV002</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sản xuất</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Đóng gói</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Khối A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Đội nhóm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Đội Ví dụ 01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Kéo co</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lê Văn C</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NV003</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sản xuất</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Kho</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Khối A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Cá nhân</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn C</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Cầu lông</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>NV003</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chạy Marathon</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn D</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NV004</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Văn phòng</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Nhân sự</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Khối văn phòng</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -578,65 +661,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>HƯỚNG DẪN NHẬP DANH SÁCH</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>1. Không sửa tên hàng tiêu đề ở dòng 1 của sheet DS_DANG_KY.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. Không sửa tên hàng tiêu đề ở dòng 1.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2. Hình thức đăng ký: Đội nhóm hoặc Cá nhân.</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2. Mỗi dòng là MỘT thành viên. Các thành viên cùng đội phải lặp lại đúng Tên Đội và Môn thi đấu.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>3. Môn thi đấu phải khớp tên môn đã tạo trong trang Admin.</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3. Khi nhập, hệ thống tự gộp các dòng cùng Hình thức + Tên Đội + Môn thành một đăng ký đội.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>4. Xóa hai dòng ví dụ trước khi nhập dữ liệu thật.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4. Hình thức đăng ký: Đội nhóm hoặc Cá nhân.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>5. Với đội nhóm, nhập danh sách thành viên chi tiết; nếu dùng Mã NV / CCCD đăng ký, phân cách nhiều mã bằng dấu chấm phẩy.</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. Môn thi đấu phải khớp tên môn đã tạo trong trang Admin.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>6. Vào Admin &gt; Cài đặt &gt; chọn file &gt; Xem trước file &gt; Nhập danh sách.</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. Với đội nhóm, điền họ tên thành viên và mã NV/CCCD mỗi dòng. Phòng ban/bộ phận là tùy chọn.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>7. Hãy thử 2–3 dòng và kiểm tra trên Google Sheets trước khi nhập danh sách lớn.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7. Xóa các dòng ví dụ trước khi nhập dữ liệu thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8. Admin &gt; Cài đặt &gt; chọn file &gt; Xem trước file &gt; Nhập danh sách.</t>
         </is>
       </c>
     </row>

--- a/Mau_Import_Dang_Ky_Hoi_Thao.xlsx
+++ b/Mau_Import_Dang_Ky_Hoi_Thao.xlsx
@@ -42,7 +42,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D6EFD"/>
+        <fgColor rgb="00174A7E"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +58,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,16 +438,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Hình thức đăng ký</t>
@@ -447,7 +455,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tên Đội / Cá nhân đăng ký</t>
+          <t>Tên đội</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -494,7 +502,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kéo co</t>
+          <t>Bóng đá</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -536,7 +544,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kéo co</t>
+          <t>Bóng đá</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -578,7 +586,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kéo co</t>
+          <t>Bóng đá</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -613,19 +621,15 @@
           <t>Cá nhân</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Nguyễn Văn D</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chạy Marathon</t>
+          <t>Cầu lông</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nguyễn Văn D</t>
+          <t>Phạm Thị D</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -661,72 +665,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>HƯỚNG DẪN NHẬP DANH SÁCH</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1. Không sửa tên hàng tiêu đề ở dòng 1.</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Mỗi dòng là MỘT thành viên đội hoặc MỘT đăng ký cá nhân.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2. Mỗi dòng là MỘT thành viên. Các thành viên cùng đội phải lặp lại đúng Tên Đội và Môn thi đấu.</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Với đội nhóm: lặp lại chính xác Tên đội và Môn thi đấu trên tất cả các dòng thành viên cùng đội.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3. Khi nhập, hệ thống tự gộp các dòng cùng Hình thức + Tên Đội + Môn thành một đăng ký đội.</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Không nhập nhiều thành viên trong cùng một ô. Mỗi người một dòng riêng.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4. Hình thức đăng ký: Đội nhóm hoặc Cá nhân.</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Hình thức đăng ký chỉ nhập Đội nhóm hoặc Cá nhân.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5. Môn thi đấu phải khớp tên môn đã tạo trong trang Admin.</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Mã NV/CCCD là mã định danh của từng thành viên; không bắt buộc nếu hệ thống của bạn cho phép bỏ trống.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6. Với đội nhóm, điền họ tên thành viên và mã NV/CCCD mỗi dòng. Phòng ban/bộ phận là tùy chọn.</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Tên môn thi đấu phải khớp tên môn đã được tạo trong trang Admin.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7. Xóa các dòng ví dụ trước khi nhập dữ liệu thật.</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Xóa các dòng ví dụ trước khi nhập dữ liệu thật, giữ nguyên hàng tiêu đề.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8. Admin &gt; Cài đặt &gt; chọn file &gt; Xem trước file &gt; Nhập danh sách.</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Trên trang Admin &gt; Cài đặt: chọn file → Xem trước file → kiểm tra số đội/thành viên → Nhập danh sách.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Các dòng có cùng Tên đội + Môn thi đấu sẽ được gộp thành một đăng ký đội. Các dòng cá nhân không bị gộp.</t>
         </is>
       </c>
     </row>

--- a/Mau_Import_Dang_Ky_Hoi_Thao.xlsx
+++ b/Mau_Import_Dang_Ky_Hoi_Thao.xlsx
@@ -42,7 +42,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00174A7E"/>
+        <fgColor rgb="000D6EFD"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,17 +58,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,16 +430,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Hình thức đăng ký</t>
@@ -455,7 +447,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tên đội</t>
+          <t>Tên Đội / Cá nhân đăng ký</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -502,7 +494,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bóng đá</t>
+          <t>Kéo co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -544,7 +536,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bóng đá</t>
+          <t>Kéo co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -586,7 +578,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bóng đá</t>
+          <t>Kéo co</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -621,15 +613,19 @@
           <t>Cá nhân</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn D</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cầu lông</t>
+          <t>Chạy Marathon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phạm Thị D</t>
+          <t>Nguyễn Văn D</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -665,79 +661,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>HƯỚNG DẪN NHẬP DANH SÁCH</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Mỗi dòng là MỘT thành viên đội hoặc MỘT đăng ký cá nhân.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. Không sửa tên hàng tiêu đề ở dòng 1.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Với đội nhóm: lặp lại chính xác Tên đội và Môn thi đấu trên tất cả các dòng thành viên cùng đội.</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2. Mỗi dòng là MỘT thành viên. Các thành viên cùng đội phải lặp lại đúng Tên Đội và Môn thi đấu.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Không nhập nhiều thành viên trong cùng một ô. Mỗi người một dòng riêng.</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3. Khi nhập, hệ thống tự gộp các dòng cùng Hình thức + Tên Đội + Môn thành một đăng ký đội.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Hình thức đăng ký chỉ nhập Đội nhóm hoặc Cá nhân.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4. Hình thức đăng ký: Đội nhóm hoặc Cá nhân.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Mã NV/CCCD là mã định danh của từng thành viên; không bắt buộc nếu hệ thống của bạn cho phép bỏ trống.</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. Môn thi đấu phải khớp tên môn đã tạo trong trang Admin.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Tên môn thi đấu phải khớp tên môn đã được tạo trong trang Admin.</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. Với đội nhóm, điền họ tên thành viên và mã NV/CCCD mỗi dòng. Phòng ban/bộ phận là tùy chọn.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Xóa các dòng ví dụ trước khi nhập dữ liệu thật, giữ nguyên hàng tiêu đề.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7. Xóa các dòng ví dụ trước khi nhập dữ liệu thật.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Trên trang Admin &gt; Cài đặt: chọn file → Xem trước file → kiểm tra số đội/thành viên → Nhập danh sách.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Các dòng có cùng Tên đội + Môn thi đấu sẽ được gộp thành một đăng ký đội. Các dòng cá nhân không bị gộp.</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8. Admin &gt; Cài đặt &gt; chọn file &gt; Xem trước file &gt; Nhập danh sách.</t>
         </is>
       </c>
     </row>
